--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,59 +662,55 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,20 +740,20 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -765,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -821,24 +817,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -855,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 97,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -967,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,47 +1108,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,33 +1323,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1478,24 +1478,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>33</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1624,11 +1624,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1731,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1770,11 +1770,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1842,51 +1842,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1911,20 +1907,20 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 84,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1933,11 +1929,11 @@
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1954,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1984,7 +1980,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1992,10 +1988,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2004,39 +1998,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,33 +2053,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2134,7 +2126,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2142,10 +2134,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2154,39 +2144,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2211,33 +2199,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2254,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2331,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2361,33 +2349,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2404,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2481,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2511,33 +2499,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2554,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2631,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2661,33 +2649,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2704,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2781,12 +2769,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2811,7 +2799,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2820,16 +2808,16 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2854,12 +2842,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2931,12 +2919,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2970,11 +2958,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3004,12 +2992,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3081,12 +3069,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3111,25 +3099,25 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3154,12 +3142,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3231,12 +3219,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3261,33 +3249,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3304,12 +3292,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3381,12 +3369,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3411,33 +3399,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3454,12 +3442,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3531,12 +3519,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3561,7 +3549,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3570,7 +3558,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3579,15 +3567,15 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3604,12 +3592,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3681,12 +3669,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3754,12 +3742,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3784,7 +3772,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3792,8 +3780,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3802,37 +3792,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3862,20 +3854,20 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3883,7 +3875,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3900,12 +3892,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3938,47 +3930,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4003,33 +3999,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 76,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4046,12 +4042,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4076,7 +4072,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4084,8 +4080,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4094,37 +4092,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4149,33 +4149,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4230,10 +4230,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4242,39 +4240,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4302,22 +4298,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4325,7 +4321,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4342,12 +4338,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4372,7 +4368,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4380,51 +4376,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4449,33 +4441,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,5%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4492,12 +4484,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4531,7 +4523,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4565,12 +4557,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4595,33 +4587,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>55</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4638,12 +4630,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4668,7 +4660,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4676,47 +4668,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4741,33 +4737,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>7</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4784,12 +4780,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4814,7 +4810,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4822,47 +4818,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4887,33 +4887,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 225,00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,6%</t>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>8</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4930,12 +4930,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5033,33 +5033,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 529,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5114,51 +5114,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5183,33 +5179,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>490</v>
+        <v>205</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,4%</t>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5226,12 +5222,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5256,7 +5252,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5264,51 +5260,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5333,33 +5325,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,2%</t>
+        <v>22</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5376,12 +5368,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5406,7 +5398,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5414,10 +5406,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5426,39 +5416,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5483,33 +5471,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>307</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5526,12 +5514,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5603,12 +5591,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5633,33 +5621,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>490</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5676,12 +5664,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5753,12 +5741,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5783,33 +5771,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+          <t>R$ 1.165,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,9%</t>
+        <v>444</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5826,12 +5814,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5903,12 +5891,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5933,25 +5921,25 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
+          <t>R$ 647,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,5%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>349</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5959,7 +5947,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5976,12 +5964,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6053,12 +6041,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6083,33 +6071,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
+          <t>R$ 324,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>121</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6126,82 +6114,532 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 340,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -665,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -967,20 +967,20 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,10 +1108,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1120,41 +1118,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1177,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1250,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1258,8 +1254,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1268,39 +1266,41 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1326,22 +1326,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 97,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1366,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1407,9 +1407,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1469,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,14 +1512,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1624,24 +1624,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1731,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1764,17 +1764,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1877,14 +1877,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1907,33 +1907,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,14 +2023,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2062,24 +2062,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,14 +2096,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2202,17 +2202,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,14 +2242,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,10 +2280,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2292,41 +2290,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2349,33 +2345,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 84,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2469,14 +2465,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2499,33 +2495,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 272,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 316,7%</t>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2619,14 +2615,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2649,33 +2645,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,12 +2688,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2769,14 +2765,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2799,12 +2795,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2817,15 +2813,15 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2842,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2919,14 +2915,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2949,12 +2945,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
@@ -2967,15 +2963,15 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2992,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3069,14 +3065,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3099,33 +3095,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3142,12 +3138,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3219,14 +3215,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3249,25 +3245,25 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3275,7 +3271,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3292,12 +3288,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3369,14 +3365,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3399,33 +3395,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3442,12 +3438,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3519,14 +3515,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3549,33 +3545,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3592,12 +3588,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3669,14 +3665,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3699,33 +3695,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3742,12 +3738,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3819,14 +3815,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3849,33 +3845,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3892,12 +3888,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3969,14 +3965,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3999,7 +3995,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4008,7 +4004,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4017,15 +4013,15 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4042,12 +4038,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4119,14 +4115,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4152,17 +4148,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4192,14 +4188,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4222,7 +4218,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4230,8 +4226,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4240,39 +4238,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4295,33 +4295,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4379,9 +4379,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4411,14 +4411,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 76,4%</t>
+        <v>11</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4484,14 +4484,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4523,11 +4523,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4557,14 +4557,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4596,16 +4596,16 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 685,7%</t>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4630,14 +4630,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4668,10 +4668,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4680,41 +4678,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4740,22 +4736,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4763,7 +4759,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4780,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4857,14 +4853,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4887,33 +4883,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,5%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4930,14 +4926,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4960,7 +4956,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4968,8 +4964,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4978,39 +4976,41 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5033,33 +5033,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
+          <t>R$ 225,00</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>▲ 67,4%</t>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5117,9 +5117,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5149,14 +5149,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5179,33 +5179,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 529,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 831,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5222,14 +5222,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5261,11 +5261,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5295,14 +5295,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5325,33 +5325,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,6%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 92,8%</t>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5368,14 +5368,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5407,11 +5407,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5441,14 +5441,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5471,33 +5471,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>307</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,3%</t>
+        <v>22</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5514,14 +5514,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5552,10 +5552,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5564,41 +5562,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5624,22 +5620,22 @@
           <t>R$ 841,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>490</v>
+        <v>307</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,4%</t>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5647,7 +5643,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,12 +5660,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5741,14 +5737,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5771,33 +5767,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
+          <t>R$ 841,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,1%</t>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,2%</t>
+        <v>490</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5814,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5891,14 +5887,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5921,33 +5917,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 1.165,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>444</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,12 +5960,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6041,14 +6037,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6071,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>121</v>
+        <v>349</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6114,12 +6110,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6191,14 +6187,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6224,22 +6220,22 @@
           <t>R$ 324,00</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,9%</t>
+        <v>121</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6247,7 +6243,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6264,12 +6260,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6341,14 +6337,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6371,33 +6367,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
+          <t>R$ 324,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,5%</t>
+          <t>▼ 44,3%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>166</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6414,12 +6410,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6491,14 +6487,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6521,33 +6517,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>251</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6564,82 +6560,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 1240,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,9 +811,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 94,0%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -967,20 +967,20 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 340,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>67</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1184,9 +1184,9 @@
       <c r="I10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,59 +1246,55 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,20 +1324,20 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1349,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1396,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1405,24 +1401,24 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1439,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1469,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 97,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1512,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1615,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1658,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1688,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1696,47 +1692,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1761,33 +1761,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1843,11 +1843,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,33 +1907,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2062,24 +2062,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>33</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2208,11 +2208,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2281,11 +2281,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2354,11 +2354,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2426,51 +2426,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2495,20 +2491,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 84,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2517,11 +2513,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2538,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2568,7 +2564,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2576,10 +2572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2588,39 +2582,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2645,33 +2637,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2688,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2718,7 +2710,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2726,10 +2718,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2738,39 +2728,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2795,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2838,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2915,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2945,33 +2933,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2988,12 +2976,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3065,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3095,33 +3083,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3138,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3215,12 +3203,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3245,33 +3233,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3288,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3365,12 +3353,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3395,7 +3383,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3404,16 +3392,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3438,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3515,12 +3503,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3554,11 +3542,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3588,12 +3576,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3665,12 +3653,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3695,25 +3683,25 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3738,12 +3726,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3815,12 +3803,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3845,33 +3833,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3888,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3965,12 +3953,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3995,33 +3983,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4038,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4115,12 +4103,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4145,7 +4133,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4154,7 +4142,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4163,15 +4151,15 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4188,12 +4176,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4265,12 +4253,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4338,12 +4326,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4368,7 +4356,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4376,8 +4364,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4386,37 +4376,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4446,20 +4438,20 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4467,7 +4459,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4484,12 +4476,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4514,7 +4506,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4522,47 +4514,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4587,33 +4583,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 76,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4630,12 +4626,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4660,7 +4656,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4668,8 +4664,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4678,37 +4676,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4733,33 +4733,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4814,10 +4814,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4826,39 +4824,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4886,22 +4882,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4909,7 +4905,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4926,12 +4922,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4956,7 +4952,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4964,51 +4960,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5033,33 +5025,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,5%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5076,12 +5068,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5115,7 +5107,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5149,12 +5141,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5179,33 +5171,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>55</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5222,12 +5214,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5252,7 +5244,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5260,47 +5252,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5325,33 +5321,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>7</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5368,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5398,7 +5394,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5406,47 +5402,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5471,33 +5471,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 225,00</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>▼ 90,6%</t>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>8</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5514,12 +5514,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5617,33 +5617,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 529,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5660,12 +5660,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5698,51 +5698,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5767,33 +5763,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>490</v>
+        <v>205</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,4%</t>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,12 +5806,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5840,7 +5836,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5848,51 +5844,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5917,33 +5909,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,2%</t>
+        <v>22</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5960,12 +5952,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5990,7 +5982,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5998,10 +5990,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6010,39 +6000,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6067,33 +6055,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>307</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,12 +6098,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6187,12 +6175,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6217,33 +6205,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>490</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6260,12 +6248,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6337,12 +6325,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6367,33 +6355,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+          <t>R$ 1.165,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,9%</t>
+        <v>444</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6410,12 +6398,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6487,12 +6475,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6517,25 +6505,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
+          <t>R$ 647,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▲ 28,5%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>349</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6543,7 +6531,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6560,12 +6548,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6637,12 +6625,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6667,33 +6655,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
+          <t>R$ 324,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>121</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6710,82 +6698,532 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,20 +739,20 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -757,11 +761,11 @@
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,47 +820,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,8 +970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>1</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -972,37 +982,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1039,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1048,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 1240,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1143,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1188,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1249,9 +1261,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -1289,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 94,0%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,7 +1404,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1405,20 +1417,20 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1477,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 340,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1486,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>67</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,7 +1559,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1581,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1622,9 +1634,9 @@
       <c r="I16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,59 +1696,55 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1766,20 +1774,20 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1787,7 +1795,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1843,24 +1851,24 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1877,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,33 +1915,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 97,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1989,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2053,33 +2061,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2096,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2126,7 +2134,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2134,47 +2142,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,33 +2211,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2242,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2281,11 +2293,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2345,33 +2357,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2427,11 +2439,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2491,7 +2503,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2500,24 +2512,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>33</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2577,7 +2589,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2646,11 +2658,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2680,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2719,11 +2731,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2792,11 +2804,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2868,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2864,51 +2876,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2933,20 +2941,20 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 84,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2955,11 +2963,11 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2976,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3006,7 +3014,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3014,10 +3022,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3026,39 +3032,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3083,33 +3087,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3126,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3156,7 +3160,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3164,10 +3168,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3176,39 +3178,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3233,33 +3233,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3383,33 +3383,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3533,33 +3533,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3683,33 +3683,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3842,16 +3842,16 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3876,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3992,11 +3992,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4133,25 +4133,25 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4176,12 +4176,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4283,33 +4283,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4433,33 +4433,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4476,12 +4476,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4601,15 +4601,15 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4814,8 +4814,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4824,37 +4826,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4884,20 +4888,20 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4905,7 +4909,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4922,12 +4926,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4952,7 +4956,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4960,47 +4964,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5025,33 +5033,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 76,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5068,12 +5076,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5098,7 +5106,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5106,8 +5114,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5116,37 +5126,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5171,33 +5183,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5214,12 +5226,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5244,7 +5256,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5252,10 +5264,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5264,39 +5274,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5324,22 +5332,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5347,7 +5355,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5364,12 +5372,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5394,7 +5402,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5402,51 +5410,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5471,33 +5475,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,5%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5514,12 +5518,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5553,7 +5557,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5587,12 +5591,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5617,33 +5621,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>55</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5660,12 +5664,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5690,7 +5694,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5698,47 +5702,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5763,33 +5771,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>7</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5806,12 +5814,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5836,7 +5844,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5844,47 +5852,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5909,33 +5921,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 225,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▼ 90,6%</t>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>8</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5952,12 +5964,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5991,7 +6003,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6013,7 +6025,7 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -6025,12 +6037,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6055,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 529,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6098,12 +6110,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6128,7 +6140,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6136,51 +6148,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6205,33 +6213,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>490</v>
+        <v>205</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,4%</t>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6248,12 +6256,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6278,7 +6286,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6286,51 +6294,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6355,33 +6359,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 27,2%</t>
+        <v>22</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6398,12 +6402,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6428,7 +6432,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6436,10 +6440,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6448,39 +6450,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6505,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>307</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6625,12 +6625,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6655,33 +6655,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>490</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6805,33 +6805,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+          <t>R$ 1.165,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,9%</t>
+        <v>444</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6955,25 +6955,25 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
+          <t>R$ 647,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▲ 28,5%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>349</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7105,33 +7105,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
+          <t>R$ 324,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>121</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7148,82 +7148,532 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
+          <t>R$ 272,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -739,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -889,33 +885,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1039,33 +1035,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1112,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,8 +1116,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1130,39 +1128,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1194,24 +1194,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1269,9 +1269,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1301,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1334,17 +1334,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1374,14 +1374,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1447,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1477,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1240,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,14 +1520,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1623,33 +1623,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 340,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,14 +1666,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1699,17 +1699,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1769,33 +1769,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1842,33 +1842,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1885,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1924,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1937,11 +1937,11 @@
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2001,20 +2001,20 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2031,14 +2031,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2064,17 +2064,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2142,10 +2142,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2154,41 +2152,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2211,33 +2207,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2254,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2284,7 +2280,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2292,8 +2288,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2302,39 +2300,41 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2360,22 +2360,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 97,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2400,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2441,9 +2441,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2473,14 +2473,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2503,33 +2503,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2546,14 +2546,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2585,11 +2585,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2619,14 +2619,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2658,24 +2658,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2765,14 +2765,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2798,17 +2798,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2911,14 +2911,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2941,33 +2941,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3057,14 +3057,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3096,24 +3096,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3130,14 +3130,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3203,14 +3203,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3236,17 +3236,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3276,14 +3276,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3314,10 +3314,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3326,41 +3324,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3383,33 +3379,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 84,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3426,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3503,14 +3499,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3533,33 +3529,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3576,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3653,14 +3649,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3683,33 +3679,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3726,12 +3722,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3803,14 +3799,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3833,12 +3829,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3851,15 +3847,15 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3876,12 +3872,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3953,14 +3949,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3983,12 +3979,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -4001,15 +3997,15 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4026,12 +4022,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4103,14 +4099,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4133,33 +4129,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4176,12 +4172,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4253,14 +4249,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4283,25 +4279,25 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4309,7 +4305,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4326,12 +4322,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4403,14 +4399,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4433,33 +4429,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4476,12 +4472,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4553,14 +4549,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4583,33 +4579,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4626,12 +4622,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,14 +4699,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4733,33 +4729,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4776,12 +4772,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4853,14 +4849,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4883,33 +4879,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4926,12 +4922,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5003,14 +4999,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5033,7 +5029,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5042,7 +5038,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5051,15 +5047,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5076,12 +5072,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5153,14 +5149,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5186,17 +5182,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5226,14 +5222,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5256,7 +5252,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5264,8 +5260,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5274,39 +5272,41 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5329,33 +5329,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5413,9 +5413,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5445,14 +5445,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5484,16 +5484,16 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 76,4%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5518,14 +5518,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5557,11 +5557,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5591,14 +5591,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,14 +5664,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5702,10 +5702,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5714,41 +5712,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5774,22 +5770,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>55</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5797,7 +5793,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5814,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5891,14 +5887,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5921,33 +5917,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▼ 57,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5964,14 +5960,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5994,7 +5990,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6002,8 +5998,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6012,39 +6010,41 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6067,33 +6067,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 225,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6151,9 +6151,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6183,14 +6183,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6213,33 +6213,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 529,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6256,14 +6256,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6295,11 +6295,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6329,14 +6329,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6359,33 +6359,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 90,6%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>205</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6402,14 +6402,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6441,11 +6441,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6475,14 +6475,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6505,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>307</v>
+        <v>22</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,14 +6548,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6586,10 +6586,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6598,41 +6596,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6658,22 +6654,22 @@
           <t>R$ 841,00</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>490</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 10,4%</t>
+        <v>307</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6681,7 +6677,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6698,12 +6694,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6775,14 +6771,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6805,33 +6801,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,2%</t>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6848,12 +6844,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6925,14 +6921,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6955,33 +6951,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
+          <t>R$ 1.165,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▲ 99,7%</t>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>349</v>
+        <v>444</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 188,4%</t>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6998,12 +6994,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7075,14 +7071,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7105,33 +7101,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>349</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7148,12 +7144,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7225,14 +7221,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7258,22 +7254,22 @@
           <t>R$ 324,00</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,9%</t>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7281,7 +7277,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7298,12 +7294,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7375,14 +7371,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7405,33 +7401,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▲ 28,5%</t>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 33,9%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7448,12 +7444,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7525,14 +7521,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7555,33 +7551,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>251</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7598,82 +7594,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 640,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -828,39 +826,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 272,00</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -966,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -978,39 +972,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1035,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1078,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1155,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1188,22 +1180,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1211,7 +1203,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1228,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1258,7 +1250,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1266,8 +1258,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1276,37 +1270,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1331,33 +1327,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1374,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,7 +1400,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1412,47 +1408,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,33 +1477,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 94,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1593,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1632,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1240,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1707,9 +1707,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1845,17 +1845,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 340,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1924,24 +1924,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1997,24 +1997,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2064,17 +2064,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,33 +2207,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2288,51 +2288,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2357,12 +2353,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -2370,20 +2366,20 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2400,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2439,7 +2435,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2473,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2503,33 +2499,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 97,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2546,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2576,7 +2572,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2584,47 +2580,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,33 +2649,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2731,11 +2731,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2795,33 +2795,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2877,11 +2877,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2941,33 +2941,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3098,22 +3098,22 @@
       <c r="I36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3236,17 +3236,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3315,11 +3315,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3379,33 +3379,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3460,10 +3460,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3472,39 +3470,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3529,33 +3525,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 84,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3572,12 +3568,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3602,7 +3598,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3610,10 +3606,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3622,39 +3616,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3679,33 +3671,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3722,12 +3714,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3799,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3829,33 +3821,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3872,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3949,12 +3941,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3982,22 +3974,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4005,7 +3997,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4022,12 +4014,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4099,12 +4091,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4129,12 +4121,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -4147,15 +4139,15 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4172,12 +4164,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4249,12 +4241,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4282,17 +4274,17 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4305,7 +4297,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4322,12 +4314,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4399,12 +4391,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4429,33 +4421,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4472,12 +4464,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4549,12 +4541,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4579,33 +4571,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4622,12 +4614,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4699,12 +4691,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4738,16 +4730,16 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4755,7 +4747,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4772,12 +4764,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4849,12 +4841,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4882,17 +4874,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4922,12 +4914,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4999,12 +4991,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5029,7 +5021,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5038,7 +5030,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5047,15 +5039,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5072,12 +5064,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5149,12 +5141,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5182,17 +5174,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5222,12 +5214,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5299,12 +5291,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5329,33 +5321,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5372,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5402,7 +5394,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5410,8 +5402,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5420,37 +5414,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5475,33 +5471,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5518,12 +5514,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5548,7 +5544,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5556,47 +5552,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5621,33 +5621,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 76,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5737,12 +5737,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5776,16 +5776,16 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 685,7%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5848,51 +5848,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5920,22 +5916,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>13</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5943,7 +5939,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5960,12 +5956,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5990,7 +5986,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5998,10 +5994,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6010,39 +6004,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6067,33 +6059,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,5%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>55</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6110,12 +6102,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6140,7 +6132,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6148,8 +6140,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6158,37 +6152,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6213,33 +6209,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▲ 67,4%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6256,12 +6252,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6286,7 +6282,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6294,47 +6290,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6359,33 +6359,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 225,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>8</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6402,12 +6402,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6441,11 +6441,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6505,33 +6505,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 529,00</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>▼ 90,6%</t>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6587,11 +6587,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6651,33 +6651,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>307</v>
+        <v>205</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,12 +6694,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6732,51 +6732,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6801,33 +6797,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>490</v>
+        <v>22</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,4%</t>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6844,12 +6840,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6874,7 +6870,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6882,10 +6878,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6894,39 +6888,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6951,33 +6943,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>444</v>
+        <v>307</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 27,2%</t>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6994,12 +6986,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7071,12 +7063,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7101,33 +7093,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
+          <t>R$ 841,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>▲ 99,7%</t>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>490</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7144,12 +7136,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7221,12 +7213,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7251,33 +7243,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 1.165,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>121</v>
+        <v>444</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7294,12 +7286,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7371,12 +7363,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7401,33 +7393,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
+          <t>R$ 647,00</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,3%</t>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>166</v>
+        <v>349</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,9%</t>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7444,12 +7436,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7521,12 +7513,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7551,33 +7543,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▲ 28,5%</t>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>121</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7594,12 +7586,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7671,12 +7663,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7701,33 +7693,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>166</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7744,82 +7736,382 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,55 +589,59 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +666,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +674,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +686,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,55 +743,59 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +820,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,8 +828,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -826,37 +840,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,55 +897,59 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 640,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +974,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,8 +982,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -972,37 +994,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,16 +1051,18 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1045,37 +1071,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1147,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,20 +1205,20 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1199,11 +1227,11 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,12 +1248,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1297,12 +1325,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,33 +1355,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,12 +1398,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1447,12 +1475,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,7 +1505,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1485,47 +1513,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,7 +1582,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1558,8 +1590,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1568,37 +1602,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1632,11 +1668,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,12 +1702,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1696,7 +1732,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1704,47 +1740,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1772,17 +1812,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1812,12 +1852,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1842,7 +1882,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1850,8 +1890,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>1</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1860,37 +1902,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,33 +1959,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1240,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +2002,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,7 +2032,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1996,8 +2040,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2006,37 +2052,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,16 +2109,16 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2079,15 +2127,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,12 +2152,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2134,55 +2182,59 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,7 +2259,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2218,9 +2270,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2229,11 +2281,11 @@
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2302,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2280,7 +2332,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2288,47 +2340,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2356,17 +2412,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2396,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2435,7 +2491,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2469,12 +2525,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2499,33 +2555,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2542,12 +2598,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2572,7 +2628,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2580,10 +2636,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2592,39 +2646,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,33 +2701,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2765,12 +2817,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2795,33 +2847,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 97,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2838,12 +2890,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2868,7 +2920,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2876,47 +2928,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2941,33 +2997,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2984,12 +3040,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3014,7 +3070,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3022,47 +3078,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>1</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3087,33 +3147,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3130,12 +3190,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3160,7 +3220,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3168,47 +3228,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>1</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3233,33 +3297,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3276,12 +3340,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3315,11 +3379,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3349,12 +3413,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3379,7 +3443,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3388,24 +3452,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3422,12 +3486,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3461,11 +3525,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3495,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3528,17 +3592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3568,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3607,7 +3671,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3641,12 +3705,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3671,33 +3735,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 340,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>67</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3714,12 +3778,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3744,7 +3808,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3752,10 +3816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3764,39 +3826,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3821,33 +3881,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 84,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3864,12 +3924,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3894,59 +3954,55 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3974,22 +4030,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4014,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4044,7 +4100,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4052,51 +4108,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4121,33 +4173,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4164,12 +4216,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4194,7 +4246,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4202,10 +4254,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4214,39 +4264,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4271,33 +4319,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4314,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,12 +4439,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4421,33 +4469,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4464,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4494,7 +4542,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4502,10 +4550,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4514,39 +4560,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4576,20 +4620,20 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4597,7 +4641,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4614,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4644,7 +4688,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4652,51 +4696,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4721,7 +4761,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4730,24 +4770,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4764,12 +4804,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4794,7 +4834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4802,51 +4842,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4874,9 +4910,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -4884,7 +4920,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 94,4%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4914,12 +4950,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4944,7 +4980,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4952,51 +4988,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5021,33 +5053,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5064,12 +5096,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5094,7 +5126,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5102,51 +5134,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5171,33 +5199,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5214,12 +5242,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5244,7 +5272,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5252,10 +5280,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5264,39 +5290,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5321,7 +5345,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5330,24 +5354,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5364,12 +5388,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5394,7 +5418,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5402,10 +5426,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5414,39 +5436,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5474,17 +5494,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5514,12 +5534,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5591,12 +5611,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5621,33 +5641,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5664,12 +5684,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5694,7 +5714,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5702,8 +5722,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5712,37 +5734,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5767,33 +5791,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>25</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5810,12 +5834,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5840,7 +5864,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5848,47 +5872,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5913,25 +5941,25 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 76,4%</t>
-        </is>
-      </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5939,7 +5967,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5956,12 +5984,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5986,7 +6014,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5994,8 +6022,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6004,37 +6034,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6059,33 +6091,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
-        </is>
-      </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6102,12 +6134,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6179,12 +6211,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6209,33 +6241,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6252,12 +6284,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6329,12 +6361,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6359,33 +6391,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,5%</t>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6402,12 +6434,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6432,7 +6464,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6440,8 +6472,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6450,37 +6484,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6505,33 +6541,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6548,12 +6584,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6578,7 +6614,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6586,47 +6622,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6651,33 +6691,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6694,12 +6734,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6724,7 +6764,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6732,47 +6772,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6800,22 +6844,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,6%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6823,7 +6867,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6840,12 +6884,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6870,7 +6914,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6878,8 +6922,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>3</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6888,37 +6934,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6943,33 +6991,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6986,12 +7034,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7063,12 +7111,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7093,33 +7141,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>490</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7136,12 +7184,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7213,12 +7261,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7243,33 +7291,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7286,12 +7334,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7363,12 +7411,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7393,33 +7441,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7436,12 +7484,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7466,7 +7514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7474,10 +7522,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7486,39 +7532,37 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7543,7 +7587,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7552,24 +7596,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7586,12 +7630,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7616,7 +7660,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7624,51 +7668,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7693,33 +7733,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,9%</t>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7736,12 +7776,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7766,7 +7806,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7774,10 +7814,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7786,39 +7824,37 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7843,20 +7879,20 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,5%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>55</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7865,11 +7901,11 @@
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7886,12 +7922,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7963,12 +7999,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7993,33 +8029,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8036,82 +8072,1866 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 225,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,5%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 529,00</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,4%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 831,8%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 92,8%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.165,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,2%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1213,8 +1213,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1223,37 +1225,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1325,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1355,7 +1359,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1363,8 +1367,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1373,37 +1379,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1475,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1552,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1629,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1659,7 +1667,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1667,8 +1675,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1677,37 +1687,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1779,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1809,7 +1821,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1817,47 +1829,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1929,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1962,17 +1978,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2002,12 +2018,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2079,12 +2095,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2109,7 +2125,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2118,7 +2134,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2127,15 +2143,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2152,12 +2168,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2229,12 +2245,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2259,7 +2275,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2267,8 +2283,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2277,37 +2295,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2379,12 +2399,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2409,55 +2429,59 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2482,7 +2506,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2490,8 +2514,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2500,37 +2526,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2555,33 +2583,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2598,12 +2626,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2628,7 +2656,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2636,8 +2664,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2646,37 +2676,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2701,55 +2733,59 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 640,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2774,7 +2810,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2782,8 +2818,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2792,37 +2830,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2847,16 +2887,18 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2865,37 +2907,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>3</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2967,12 +3011,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2997,55 +3041,59 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3117,12 +3165,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3147,55 +3195,59 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3267,12 +3319,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3297,7 +3349,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3305,47 +3357,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3370,7 +3426,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3378,8 +3434,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3388,37 +3446,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3443,7 +3503,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3451,47 +3511,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>4</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3516,7 +3580,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3524,47 +3588,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3589,55 +3657,59 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3662,7 +3734,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3670,8 +3742,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3680,37 +3754,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3735,7 +3811,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3743,47 +3819,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1240,0%</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3808,7 +3888,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3816,8 +3896,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3826,37 +3908,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3881,16 +3965,18 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3899,37 +3985,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3954,55 +4042,59 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4027,7 +4119,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4035,47 +4127,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4100,7 +4196,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4108,47 +4204,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4173,7 +4273,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4181,47 +4281,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4246,7 +4350,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4254,8 +4358,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>1</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4264,37 +4370,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4322,17 +4430,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4362,12 +4470,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4439,12 +4547,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4469,33 +4577,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4512,12 +4620,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4542,7 +4650,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4550,8 +4658,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4560,37 +4670,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4615,55 +4727,59 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 97,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4688,7 +4804,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4696,47 +4812,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4761,7 +4881,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4770,24 +4890,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4804,12 +4924,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4834,7 +4954,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4842,47 +4962,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>1</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4916,11 +5040,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4950,12 +5074,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4980,7 +5104,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4988,47 +5112,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5062,11 +5190,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5096,12 +5224,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5126,7 +5254,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5134,47 +5262,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5225,7 +5357,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5242,12 +5374,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5272,7 +5404,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5280,8 +5412,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>1</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5290,37 +5424,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5356,9 +5492,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5388,12 +5524,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5418,7 +5554,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5426,8 +5562,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5436,37 +5574,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5500,11 +5640,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5534,12 +5674,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5564,7 +5704,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5572,10 +5712,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5584,39 +5722,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5641,33 +5777,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 84,0%</t>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5684,12 +5820,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5714,7 +5850,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5722,10 +5858,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5734,39 +5868,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5791,33 +5923,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 316,7%</t>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5834,12 +5966,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5864,7 +5996,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5872,10 +6004,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5884,39 +6014,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5941,33 +6069,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 204,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5984,12 +6112,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6061,12 +6189,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6094,22 +6222,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6117,7 +6245,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6134,12 +6262,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6211,12 +6339,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6241,33 +6369,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6284,12 +6412,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6361,12 +6489,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6394,22 +6522,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,9%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6417,7 +6545,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6434,12 +6562,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6464,7 +6592,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6472,10 +6600,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6484,39 +6610,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6541,7 +6665,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6550,24 +6674,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6584,12 +6708,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6614,7 +6738,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6622,51 +6746,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6700,11 +6820,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 94,4%</t>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6734,12 +6854,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6764,7 +6884,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6772,10 +6892,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6784,39 +6902,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6841,7 +6957,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 340,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6850,24 +6966,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6884,12 +7000,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6914,7 +7030,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6922,10 +7038,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6934,39 +7048,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7000,11 +7112,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7034,12 +7146,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7064,59 +7176,55 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7141,7 +7249,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7150,24 +7258,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7184,12 +7292,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7214,7 +7322,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7222,51 +7330,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7300,11 +7404,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7334,12 +7438,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7364,7 +7468,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7372,10 +7476,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7384,39 +7486,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7450,11 +7550,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7484,12 +7584,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7514,7 +7614,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7522,8 +7622,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7532,37 +7634,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7587,7 +7691,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7596,24 +7700,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>3</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7630,12 +7734,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7671,9 +7775,9 @@
       <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7703,12 +7807,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7733,33 +7837,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 76,4%</t>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7776,12 +7880,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7815,11 +7919,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7849,12 +7953,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7879,25 +7983,25 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 685,7%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -7905,7 +8009,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7922,12 +8026,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7952,7 +8056,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7960,51 +8064,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8029,33 +8129,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8072,12 +8172,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8102,7 +8202,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8110,51 +8210,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8179,33 +8275,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8222,12 +8318,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8261,11 +8357,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8295,12 +8391,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8325,33 +8421,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8368,12 +8464,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8407,11 +8503,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8441,12 +8537,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8471,33 +8567,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8514,12 +8610,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8553,11 +8649,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8587,12 +8683,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8617,33 +8713,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▼ 92,8%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8660,12 +8756,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8690,7 +8786,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8698,8 +8794,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>3</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8708,37 +8806,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8763,33 +8863,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>307</v>
+        <v>4</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8806,12 +8906,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8883,12 +8983,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8913,33 +9013,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,8%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>490</v>
+        <v>25</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,4%</t>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8956,12 +9056,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9033,12 +9133,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9063,33 +9163,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27,2%</t>
+        <v>6</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9106,12 +9206,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9183,12 +9283,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9213,33 +9313,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9256,12 +9356,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9333,12 +9433,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9363,33 +9463,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
-        </is>
-      </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9406,12 +9506,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9483,12 +9583,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9513,33 +9613,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,3%</t>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,9%</t>
+        <v>6</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9556,12 +9656,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9633,12 +9733,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9663,33 +9763,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,5%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9706,12 +9806,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9783,12 +9883,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9813,33 +9913,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9856,82 +9956,3204 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 225,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,5%</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 529,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,4%</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 831,8%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 92,8%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 1.165,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,1%</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,2%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,90</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 67,90</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">

--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,14 +1945,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1983,8 +1983,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1993,37 +1995,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2095,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2168,12 +2172,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2245,14 +2249,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2275,7 +2279,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2283,10 +2287,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2295,39 +2297,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2553,14 +2553,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2591,8 +2591,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2601,37 +2603,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2703,14 +2707,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2733,7 +2737,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2741,10 +2745,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2753,39 +2755,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2934,12 +2934,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3704,12 +3704,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4397,14 +4397,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4435,8 +4435,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4445,37 +4447,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4547,12 +4551,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4620,12 +4624,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4697,14 +4701,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4727,7 +4731,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4735,10 +4739,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4747,39 +4749,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4851,14 +4851,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4889,8 +4889,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4899,37 +4901,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5001,12 +5005,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5042,9 +5046,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -5074,12 +5078,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5151,14 +5155,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5184,17 +5188,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5224,12 +5228,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5301,14 +5305,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5331,12 +5335,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -5344,20 +5348,20 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5374,12 +5378,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5451,14 +5455,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5481,7 +5485,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5490,7 +5494,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5499,15 +5503,15 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5524,12 +5528,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5601,14 +5605,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5634,17 +5638,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5674,14 +5678,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5704,7 +5708,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5712,8 +5716,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5722,39 +5728,41 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5777,33 +5785,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 91,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5820,12 +5828,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5893,14 +5901,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5923,33 +5931,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 640,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5966,12 +5974,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6039,14 +6047,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6069,33 +6077,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
+          <t>R$ 272,00</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6112,14 +6120,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6142,7 +6150,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6150,10 +6158,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6162,41 +6168,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6219,33 +6223,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6262,12 +6266,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6339,14 +6343,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6369,33 +6373,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6412,12 +6416,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6489,14 +6493,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6519,33 +6523,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6562,14 +6566,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6592,7 +6596,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6600,8 +6604,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6610,39 +6616,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6665,7 +6673,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6674,24 +6682,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6708,12 +6716,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6749,9 +6757,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6781,14 +6789,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6814,17 +6822,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6854,14 +6862,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6893,11 +6901,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6927,14 +6935,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6957,33 +6965,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1240,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7000,14 +7008,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7039,7 +7047,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -7073,14 +7081,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7103,33 +7111,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 340,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7146,14 +7154,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7179,17 +7187,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7219,14 +7227,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7249,33 +7257,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7292,14 +7300,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7322,33 +7330,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7365,14 +7373,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7395,7 +7403,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7404,11 +7412,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7417,11 +7425,11 @@
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7438,14 +7446,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7468,7 +7476,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7481,20 +7489,20 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7511,14 +7519,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7544,17 +7552,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7584,14 +7592,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7614,7 +7622,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7622,10 +7630,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7634,41 +7640,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7691,33 +7695,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7734,14 +7738,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7764,7 +7768,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7772,8 +7776,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7782,39 +7788,41 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7840,22 +7848,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 97,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7880,12 +7888,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7921,9 +7929,9 @@
       <c r="I99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7953,14 +7961,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7983,33 +7991,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -8026,14 +8034,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8065,11 +8073,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8099,14 +8107,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8129,7 +8137,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8138,24 +8146,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8172,12 +8180,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8245,14 +8253,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8278,17 +8286,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8318,12 +8326,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8391,14 +8399,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8421,33 +8429,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8464,12 +8472,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8507,7 +8515,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8537,14 +8545,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8567,7 +8575,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8576,24 +8584,24 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8610,14 +8618,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8649,7 +8657,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8683,14 +8691,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8716,17 +8724,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8756,14 +8764,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8786,7 +8794,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8794,10 +8802,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8806,41 +8812,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8863,33 +8867,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 84,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8906,12 +8910,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8983,14 +8987,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9013,33 +9017,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9056,12 +9060,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9133,14 +9137,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9163,33 +9167,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9206,12 +9210,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9283,14 +9287,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9313,12 +9317,12 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
@@ -9331,15 +9335,15 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9356,12 +9360,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9433,14 +9437,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9463,12 +9467,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -9481,15 +9485,15 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9506,12 +9510,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9583,14 +9587,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9613,33 +9617,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9656,12 +9660,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9733,14 +9737,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9763,25 +9767,25 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
@@ -9789,7 +9793,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9806,12 +9810,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9883,14 +9887,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9913,33 +9917,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9956,12 +9960,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10033,14 +10037,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10063,33 +10067,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10106,12 +10110,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10183,14 +10187,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10213,33 +10217,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10256,12 +10260,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10333,14 +10337,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10363,33 +10367,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10406,12 +10410,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10483,14 +10487,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10513,7 +10517,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10522,7 +10526,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10531,15 +10535,15 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10556,12 +10560,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10633,14 +10637,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10666,17 +10670,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10706,14 +10710,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10736,7 +10740,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10744,8 +10748,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10754,39 +10760,41 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10809,33 +10817,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10852,12 +10860,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10893,9 +10901,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10925,14 +10933,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10964,16 +10972,16 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 76,4%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
@@ -10981,7 +10989,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10998,14 +11006,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11037,11 +11045,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11071,14 +11079,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11110,16 +11118,16 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
@@ -11127,7 +11135,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11144,14 +11152,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11174,7 +11182,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11182,10 +11190,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I143" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11194,41 +11200,39 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11254,22 +11258,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>55</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
@@ -11277,7 +11281,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11294,12 +11298,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11371,14 +11375,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11401,33 +11405,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11444,14 +11448,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11474,7 +11478,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11482,8 +11486,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="n">
-        <v>0</v>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11492,39 +11498,41 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11547,33 +11555,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 225,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11590,12 +11598,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11631,9 +11639,9 @@
       <c r="I149" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11663,14 +11671,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11693,33 +11701,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 529,00</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11736,14 +11744,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11775,11 +11783,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11809,14 +11817,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11839,33 +11847,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,6%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>205</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11882,14 +11890,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11921,11 +11929,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11943,7 +11951,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11955,14 +11963,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11985,33 +11993,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>307</v>
+        <v>22</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12028,14 +12036,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12058,7 +12066,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12066,10 +12074,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -12078,41 +12084,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12138,22 +12142,22 @@
           <t>R$ 841,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>490</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,4%</t>
+        <v>307</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
@@ -12161,7 +12165,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12178,12 +12182,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12255,14 +12259,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12285,33 +12289,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,2%</t>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12328,12 +12332,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12405,14 +12409,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12435,33 +12439,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
+          <t>R$ 1.165,00</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,7%</t>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>349</v>
+        <v>444</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 188,4%</t>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12478,12 +12482,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12555,14 +12559,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12585,33 +12589,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>349</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12628,12 +12632,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12705,14 +12709,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12738,22 +12742,22 @@
           <t>R$ 324,00</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,9%</t>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
@@ -12761,7 +12765,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12778,12 +12782,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12855,14 +12859,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12885,33 +12889,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,5%</t>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 33,9%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12928,12 +12932,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13005,14 +13009,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -13035,33 +13039,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>251</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13078,82 +13082,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 67,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,14 +2099,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2137,8 +2137,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2147,37 +2149,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2249,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2322,12 +2326,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2399,14 +2403,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2429,7 +2433,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2437,10 +2441,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2449,39 +2451,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2707,14 +2707,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2745,8 +2745,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2755,37 +2757,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2857,14 +2861,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2887,7 +2891,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2895,10 +2899,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2907,39 +2909,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3704,12 +3704,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4474,12 +4474,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4551,14 +4551,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4589,8 +4589,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4599,37 +4601,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4701,12 +4705,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4774,12 +4778,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4851,14 +4855,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4881,7 +4885,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4889,10 +4893,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4901,39 +4903,37 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5005,14 +5005,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5043,8 +5043,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5053,37 +5055,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5155,12 +5159,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5196,9 +5200,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5228,12 +5232,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5305,14 +5309,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5338,17 +5342,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5378,12 +5382,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5455,14 +5459,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5485,12 +5489,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -5498,20 +5502,20 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5528,12 +5532,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5605,14 +5609,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5635,7 +5639,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5644,7 +5648,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5653,15 +5657,15 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5678,12 +5682,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5755,14 +5759,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5788,17 +5792,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5828,14 +5832,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5858,7 +5862,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5866,8 +5870,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5876,39 +5882,41 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5931,33 +5939,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 91,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5974,12 +5982,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6047,14 +6055,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6077,33 +6085,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 640,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6120,12 +6128,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6193,14 +6201,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6223,33 +6231,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
+          <t>R$ 272,00</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6266,14 +6274,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6296,7 +6304,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6304,10 +6312,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6316,41 +6322,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6373,33 +6377,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6416,12 +6420,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6493,14 +6497,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6523,33 +6527,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6566,12 +6570,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6643,14 +6647,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6673,33 +6677,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6716,14 +6720,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6746,7 +6750,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6754,8 +6758,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6764,39 +6770,41 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6819,7 +6827,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6828,24 +6836,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6862,12 +6870,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6903,9 +6911,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6935,14 +6943,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6968,17 +6976,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -7008,14 +7016,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7047,11 +7055,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7081,14 +7089,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7111,33 +7119,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1240,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7154,14 +7162,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7193,7 +7201,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7227,14 +7235,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7257,33 +7265,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 340,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7300,14 +7308,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7333,17 +7341,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7373,14 +7381,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7403,33 +7411,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7446,14 +7454,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7476,33 +7484,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7519,14 +7527,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7549,7 +7557,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7558,11 +7566,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7571,11 +7579,11 @@
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7592,14 +7600,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7622,7 +7630,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7635,20 +7643,20 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7665,14 +7673,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7698,17 +7706,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7738,14 +7746,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7768,7 +7776,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7776,10 +7784,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7788,41 +7794,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7845,33 +7849,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7888,14 +7892,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7918,7 +7922,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7926,8 +7930,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7936,39 +7942,41 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7994,22 +8002,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 97,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -8034,12 +8042,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8075,9 +8083,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -8107,14 +8115,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8137,33 +8145,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8180,14 +8188,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8219,11 +8227,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8253,14 +8261,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8283,7 +8291,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8292,24 +8300,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8326,12 +8334,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8399,14 +8407,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8432,17 +8440,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8472,12 +8480,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8545,14 +8553,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8575,33 +8583,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8618,12 +8626,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8661,7 +8669,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8691,14 +8699,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8721,7 +8729,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8730,24 +8738,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8764,14 +8772,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8803,7 +8811,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8837,14 +8845,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8870,17 +8878,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8910,14 +8918,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8940,7 +8948,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8948,10 +8956,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8960,41 +8966,39 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9017,33 +9021,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▼ 84,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9060,12 +9064,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9137,14 +9141,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9167,33 +9171,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9210,12 +9214,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9287,14 +9291,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9317,33 +9321,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9360,12 +9364,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9437,14 +9441,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9467,12 +9471,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -9485,15 +9489,15 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9510,12 +9514,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9587,14 +9591,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9617,12 +9621,12 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -9635,15 +9639,15 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9660,12 +9664,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9737,14 +9741,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9767,33 +9771,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9810,12 +9814,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9887,14 +9891,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9917,25 +9921,25 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
@@ -9943,7 +9947,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9960,12 +9964,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10037,14 +10041,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10067,33 +10071,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10110,12 +10114,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10187,14 +10191,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10217,33 +10221,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10260,12 +10264,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10337,14 +10341,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10367,33 +10371,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10410,12 +10414,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10487,14 +10491,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10517,33 +10521,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10560,12 +10564,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10637,14 +10641,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10667,7 +10671,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10676,7 +10680,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10685,15 +10689,15 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10710,12 +10714,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10787,14 +10791,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10820,17 +10824,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10860,14 +10864,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10890,7 +10894,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10898,8 +10902,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10908,39 +10914,41 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10963,33 +10971,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -11006,12 +11014,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11047,9 +11055,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11079,14 +11087,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11118,16 +11126,16 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 76,4%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
@@ -11135,7 +11143,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11152,14 +11160,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11191,11 +11199,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11225,14 +11233,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11264,16 +11272,16 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
@@ -11281,7 +11289,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11298,14 +11306,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11328,7 +11336,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11336,10 +11344,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11348,41 +11354,39 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11408,22 +11412,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>55</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
@@ -11431,7 +11435,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11448,12 +11452,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11525,14 +11529,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11555,33 +11559,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11598,14 +11602,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11628,7 +11632,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11636,8 +11640,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11646,39 +11652,41 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11701,33 +11709,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 225,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11744,12 +11752,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11785,9 +11793,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11817,14 +11825,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11847,33 +11855,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 529,00</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11890,14 +11898,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11929,11 +11937,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11963,14 +11971,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11993,33 +12001,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,6%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>205</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12036,14 +12044,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12075,11 +12083,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12097,7 +12105,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -12109,14 +12117,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12139,33 +12147,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>307</v>
+        <v>22</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12182,14 +12190,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12212,7 +12220,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12220,10 +12228,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12232,41 +12238,39 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12292,22 +12296,22 @@
           <t>R$ 841,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>490</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,4%</t>
+        <v>307</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12315,7 +12319,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12332,12 +12336,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12409,14 +12413,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12439,33 +12443,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,2%</t>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12482,12 +12486,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12559,14 +12563,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12589,33 +12593,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
+          <t>R$ 1.165,00</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,7%</t>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>349</v>
+        <v>444</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 188,4%</t>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12632,12 +12636,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12709,14 +12713,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12739,33 +12743,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>349</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12782,12 +12786,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12859,14 +12863,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12892,22 +12896,22 @@
           <t>R$ 324,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,9%</t>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
@@ -12915,7 +12919,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12932,12 +12936,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13009,14 +13013,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -13039,33 +13043,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,5%</t>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 33,9%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13082,12 +13086,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13159,14 +13163,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -13189,33 +13193,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>251</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13232,82 +13236,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 67,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,14 +2253,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2291,8 +2291,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2301,37 +2303,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2403,12 +2407,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2476,12 +2480,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2553,14 +2557,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2583,7 +2587,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2591,10 +2595,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2603,39 +2605,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2861,14 +2861,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2899,8 +2899,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2909,37 +2911,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3011,14 +3015,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3049,10 +3053,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3061,39 +3063,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3704,12 +3704,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4474,12 +4474,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4705,14 +4705,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4743,8 +4743,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4753,37 +4755,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4855,12 +4859,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4928,12 +4932,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5005,14 +5009,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5035,7 +5039,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5043,10 +5047,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5055,39 +5057,37 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5159,14 +5159,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5197,8 +5197,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5207,37 +5209,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5309,12 +5313,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5350,9 +5354,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5382,12 +5386,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5459,14 +5463,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5492,17 +5496,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5532,12 +5536,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5609,14 +5613,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5639,12 +5643,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -5652,20 +5656,20 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5682,12 +5686,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5759,14 +5763,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5789,7 +5793,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5798,7 +5802,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5807,15 +5811,15 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5832,12 +5836,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5909,14 +5913,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -5942,17 +5946,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5982,14 +5986,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6012,7 +6016,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -6020,8 +6024,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -6030,39 +6036,41 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6085,33 +6093,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 91,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6128,12 +6136,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6201,14 +6209,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6231,33 +6239,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 640,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6274,12 +6282,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6347,14 +6355,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6377,33 +6385,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
+          <t>R$ 272,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>37</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6420,14 +6428,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6450,7 +6458,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6458,10 +6466,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6470,41 +6476,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6527,33 +6531,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6570,12 +6574,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6647,14 +6651,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6677,33 +6681,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6720,12 +6724,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6797,14 +6801,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6827,33 +6831,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6870,14 +6874,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6900,7 +6904,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6908,8 +6912,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6918,39 +6924,41 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -6973,7 +6981,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6982,24 +6990,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7016,12 +7024,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7057,9 +7065,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7089,14 +7097,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7122,17 +7130,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7162,14 +7170,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7201,11 +7209,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7235,14 +7243,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7265,33 +7273,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1240,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7308,14 +7316,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7347,7 +7355,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7381,14 +7389,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7411,33 +7419,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 340,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>67</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7454,14 +7462,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7487,17 +7495,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7527,14 +7535,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7557,33 +7565,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7600,14 +7608,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7630,33 +7638,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7673,14 +7681,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7703,7 +7711,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7712,11 +7720,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7725,11 +7733,11 @@
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7746,14 +7754,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7776,7 +7784,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7789,20 +7797,20 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7819,14 +7827,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7852,17 +7860,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7892,14 +7900,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7922,7 +7930,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7930,10 +7938,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7942,41 +7948,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -7999,33 +8003,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -8042,14 +8046,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8072,7 +8076,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8080,8 +8084,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -8090,39 +8096,41 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8148,22 +8156,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 97,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
@@ -8188,12 +8196,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8229,9 +8237,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8261,14 +8269,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8291,33 +8299,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8334,14 +8342,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8373,11 +8381,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8407,14 +8415,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8437,7 +8445,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8446,24 +8454,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8480,12 +8488,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8553,14 +8561,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8586,17 +8594,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8626,12 +8634,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8699,14 +8707,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8729,33 +8737,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8772,12 +8780,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8815,7 +8823,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8845,14 +8853,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8875,7 +8883,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8884,24 +8892,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8918,14 +8926,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -8957,7 +8965,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8991,14 +8999,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9024,17 +9032,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -9064,14 +9072,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9094,7 +9102,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9102,10 +9110,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -9114,41 +9120,39 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9171,33 +9175,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 84,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9214,12 +9218,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9291,14 +9295,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9321,33 +9325,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9364,12 +9368,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9441,14 +9445,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9471,33 +9475,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9514,12 +9518,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9591,14 +9595,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9621,12 +9625,12 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -9639,15 +9643,15 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9664,12 +9668,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9741,14 +9745,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9771,12 +9775,12 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
@@ -9789,15 +9793,15 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9814,12 +9818,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9891,14 +9895,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -9921,33 +9925,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9964,12 +9968,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10041,14 +10045,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10071,25 +10075,25 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
@@ -10097,7 +10101,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10114,12 +10118,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10191,14 +10195,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10221,33 +10225,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10264,12 +10268,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10341,14 +10345,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10371,33 +10375,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10414,12 +10418,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10491,14 +10495,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10521,33 +10525,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10564,12 +10568,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10641,14 +10645,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10671,33 +10675,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10714,12 +10718,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10791,14 +10795,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10821,7 +10825,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10830,7 +10834,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10839,15 +10843,15 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10864,12 +10868,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10941,14 +10945,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -10974,17 +10978,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -11014,14 +11018,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11044,7 +11048,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11052,8 +11056,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11062,39 +11068,41 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11117,33 +11125,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11160,12 +11168,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11201,9 +11209,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11233,14 +11241,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11272,16 +11280,16 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▼ 76,4%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
@@ -11289,7 +11297,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11306,14 +11314,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11345,11 +11353,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11379,14 +11387,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11418,16 +11426,16 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
@@ -11435,7 +11443,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11452,14 +11460,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11482,7 +11490,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11490,10 +11498,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11502,41 +11508,39 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11562,22 +11566,22 @@
           <t>R$ 150,00</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,5%</t>
+        <v>55</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
@@ -11585,7 +11589,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11602,12 +11606,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11679,14 +11683,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11709,33 +11713,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,5%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11752,14 +11756,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11782,7 +11786,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11790,8 +11794,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>0</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11800,39 +11806,41 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -11855,33 +11863,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 225,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11898,12 +11906,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11939,9 +11947,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11971,14 +11979,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12001,33 +12009,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
+          <t>R$ 529,00</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 831,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12044,14 +12052,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12083,11 +12091,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12117,14 +12125,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12147,33 +12155,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 90,6%</t>
+          <t>R$ 316,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 92,8%</t>
+        <v>205</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12190,14 +12198,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12229,11 +12237,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12251,7 +12259,7 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -12263,14 +12271,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12293,33 +12301,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>307</v>
+        <v>22</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,3%</t>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12336,14 +12344,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12366,7 +12374,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12374,10 +12382,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12386,41 +12392,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12446,22 +12450,22 @@
           <t>R$ 841,00</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>490</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,4%</t>
+        <v>307</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
@@ -12469,7 +12473,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12486,12 +12490,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12563,14 +12567,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12593,33 +12597,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,1%</t>
+          <t>R$ 841,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,2%</t>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12636,12 +12640,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12713,14 +12717,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12743,33 +12747,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
+          <t>R$ 1.165,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,7%</t>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>349</v>
+        <v>444</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 188,4%</t>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12786,12 +12790,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12863,14 +12867,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -12893,33 +12897,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,1%</t>
+        <v>349</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12936,12 +12940,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13013,14 +13017,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -13046,22 +13050,22 @@
           <t>R$ 324,00</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,3%</t>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,9%</t>
+          <t>▼ 27,1%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -13069,7 +13073,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13086,12 +13090,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13163,14 +13167,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -13193,33 +13197,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,5%</t>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>251</v>
+        <v>166</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 33,9%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13236,12 +13240,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13313,14 +13317,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-030</t>
@@ -13343,33 +13347,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>251</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13386,82 +13390,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 67,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
+++ b/saida_skus/SKU_UTD-030-BOLEIRA-VITTAZA-COM-PE-1750.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1059,10 +1059,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1071,39 +1069,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1171,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1248,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1325,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1402,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1479,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1556,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1633,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1710,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1787,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1864,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1941,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2018,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2095,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2172,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2249,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2330,12 +2326,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2407,12 +2403,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2437,7 +2433,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2445,8 +2441,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2455,37 +2453,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2595,8 +2595,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2605,37 +2607,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2707,12 +2711,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2784,12 +2788,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2861,12 +2865,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2938,12 +2942,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3015,12 +3019,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3088,12 +3092,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,12 +3169,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3195,7 +3199,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3203,10 +3207,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3215,39 +3217,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3665,10 +3665,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3677,39 +3675,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3781,12 +3777,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3858,12 +3854,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3935,12 +3931,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4012,12 +4008,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4089,12 +4085,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4166,12 +4162,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4243,12 +4239,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4320,12 +4316,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4397,12 +4393,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4474,12 +4470,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4551,12 +4547,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4628,12 +4624,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4705,12 +4701,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4782,12 +4778,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4859,12 +4855,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4889,7 +4885,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4897,8 +4893,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4907,37 +4905,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5047,8 +5047,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5057,37 +5059,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5159,12 +5163,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5236,12 +5240,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5313,12 +5317,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5343,7 +5347,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5351,8 +5355,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5361,37 +5367,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5463,12 +5471,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5504,9 +5512,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5536,12 +5544,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5613,12 +5621,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5646,17 +5654,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5686,12 +5694,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5763,12 +5771,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5793,7 +5801,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5801,8 +5809,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>1</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5811,37 +5821,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5913,12 +5925,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5986,12 +5998,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6063,12 +6075,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6096,9 +6108,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -6136,12 +6148,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6166,7 +6178,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6174,8 +6186,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6184,37 +6198,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6239,33 +6255,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 91,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6282,12 +6298,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6312,7 +6328,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6320,8 +6336,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6330,37 +6348,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6385,33 +6405,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 640,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6428,12 +6448,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6458,7 +6478,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6466,8 +6486,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6476,37 +6498,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6531,16 +6555,16 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 204,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6549,15 +6573,15 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6574,12 +6598,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6651,12 +6675,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6681,12 +6705,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -6703,11 +6727,11 @@
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6724,12 +6748,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6754,7 +6778,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6762,10 +6786,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6774,39 +6796,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6834,22 +6854,22 @@
           <t>R$ 136,00</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 91,9%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6857,7 +6877,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6874,12 +6894,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6904,7 +6924,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6912,10 +6932,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6924,39 +6942,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6981,33 +6997,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 640,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7024,12 +7040,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7097,12 +7113,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7127,33 +7143,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 204,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7170,12 +7186,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7200,7 +7216,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7208,47 +7224,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7273,33 +7293,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,0%</t>
-        </is>
-      </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7316,12 +7336,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7346,7 +7366,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7354,8 +7374,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>1</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7364,37 +7386,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7419,33 +7443,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 340,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 1240,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7462,12 +7486,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7492,7 +7516,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7500,8 +7524,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7510,37 +7536,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7565,33 +7593,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7608,12 +7636,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7641,17 +7669,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7681,12 +7709,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7711,7 +7739,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7720,24 +7748,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7754,12 +7782,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7784,7 +7812,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7793,24 +7821,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7827,12 +7855,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7860,17 +7888,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 94,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7900,12 +7928,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7973,12 +8001,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8003,33 +8031,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 340,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 1240,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -8046,12 +8074,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8076,7 +8104,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8084,10 +8112,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -8096,39 +8122,37 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8153,33 +8177,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8196,12 +8220,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8229,17 +8253,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8269,12 +8293,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8302,22 +8326,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 97,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
@@ -8325,7 +8349,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8342,12 +8366,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8372,7 +8396,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8381,24 +8405,24 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8415,12 +8439,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8445,7 +8469,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8454,24 +8478,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8488,12 +8512,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8531,7 +8555,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8561,12 +8585,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8594,17 +8618,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8634,12 +8658,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8664,7 +8688,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8672,47 +8696,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>1</v>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8737,12 +8765,12 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
@@ -8755,15 +8783,15 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8780,12 +8808,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8819,11 +8847,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8853,12 +8881,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8886,17 +8914,17 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 97,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8909,7 +8937,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8926,12 +8954,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8965,11 +8993,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8999,12 +9027,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9029,7 +9057,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -9038,24 +9066,24 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9072,12 +9100,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9111,11 +9139,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -9145,12 +9173,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9178,17 +9206,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9218,12 +9246,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9248,7 +9276,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9256,51 +9284,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9325,33 +9349,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 272,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 84,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9368,12 +9392,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9398,7 +9422,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9406,51 +9430,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9478,22 +9498,22 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 316,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
@@ -9501,7 +9521,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9518,12 +9538,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9548,7 +9568,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9556,10 +9576,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9568,39 +9586,37 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9625,33 +9641,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9668,12 +9684,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9698,7 +9714,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9706,10 +9722,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9718,39 +9732,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9775,33 +9787,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9818,12 +9830,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9895,12 +9907,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9925,33 +9937,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 272,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 84,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9968,12 +9980,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10045,12 +10057,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10080,20 +10092,20 @@
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 316,7%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
@@ -10101,7 +10113,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10118,12 +10130,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10195,12 +10207,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10225,20 +10237,20 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10247,11 +10259,11 @@
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10268,12 +10280,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10345,12 +10357,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10375,33 +10387,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 94,4%</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10418,12 +10430,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10495,12 +10507,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10525,33 +10537,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10568,12 +10580,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10645,12 +10657,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10675,33 +10687,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 13,9%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10718,12 +10730,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10795,12 +10807,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10825,7 +10837,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10834,24 +10846,24 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10868,12 +10880,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10945,12 +10957,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10978,17 +10990,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 94,4%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -11018,12 +11030,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11095,12 +11107,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11125,33 +11137,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11168,12 +11180,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11198,7 +11210,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11206,8 +11218,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11216,37 +11230,39 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11271,33 +11287,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11314,12 +11330,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11344,7 +11360,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11352,47 +11368,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11422,20 +11442,20 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 76,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
@@ -11443,7 +11463,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11460,12 +11480,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11490,7 +11510,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11498,8 +11518,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="n">
-        <v>1</v>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11508,37 +11530,39 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11563,33 +11587,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 685,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11606,12 +11630,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11683,12 +11707,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11713,33 +11737,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 150,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11756,12 +11780,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11786,7 +11810,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11794,10 +11818,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11806,39 +11828,37 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11863,33 +11883,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 225,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,5%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11906,12 +11926,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11947,9 +11967,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11979,12 +11999,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12009,33 +12029,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 529,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 67,4%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 76,4%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12052,12 +12072,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12091,11 +12111,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12125,12 +12145,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12155,33 +12175,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 316,00</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 150,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 831,8%</t>
+          <t>▲ 685,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12198,12 +12218,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12228,7 +12248,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12236,47 +12256,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12301,33 +12325,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 150,00</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>▼ 90,6%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 92,8%</t>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12344,12 +12368,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12374,7 +12398,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12382,8 +12406,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>3</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12392,37 +12418,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12447,33 +12475,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 225,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,5%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>307</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12490,12 +12518,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12520,7 +12548,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12528,10 +12556,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12540,39 +12566,37 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12597,33 +12621,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 841,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,8%</t>
+          <t>R$ 529,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 67,4%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>490</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12640,12 +12664,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12670,7 +12694,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12678,51 +12702,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12747,33 +12767,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 1.165,00</t>
+          <t>R$ 316,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,1%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>444</v>
+        <v>205</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 27,2%</t>
+          <t>▲ 831,8%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12790,12 +12810,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12820,7 +12840,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12828,51 +12848,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12897,33 +12913,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 647,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,7%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 90,6%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>349</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 188,4%</t>
+        <v>22</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 92,8%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12940,12 +12956,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12970,7 +12986,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12978,10 +12994,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I167" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12990,39 +13004,37 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13047,7 +13059,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
+          <t>R$ 841,00</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -13056,24 +13068,24 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>121</v>
+        <v>307</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,1%</t>
+          <t>▼ 37,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13090,12 +13102,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13167,12 +13179,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13197,33 +13209,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 324,00</t>
+          <t>R$ 841,00</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,3%</t>
+          <t>▼ 27,8%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,9%</t>
+        <v>490</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13240,12 +13252,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13317,12 +13329,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13347,33 +13359,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 582,00</t>
+          <t>R$ 1.165,00</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>▲ 28,5%</t>
+          <t>▲ 80,1%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>444</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27,2%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13390,12 +13402,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13467,12 +13479,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13497,33 +13509,33 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 453,00</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 647,00</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,7%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>349</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 188,4%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13540,82 +13552,682 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,1%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 324,00</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,3%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,9%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 582,00</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,5%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>6471156914</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-030</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Boleira Vittaza- com pé-1750</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>6470982250</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 453,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Ruim</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-030</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Boleira Vittaza- com pé-1750</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>6471156914</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 67,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 67,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>